--- a/src/main/resources/data/log.xlsx
+++ b/src/main/resources/data/log.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="136">
   <si>
     <t>Function</t>
   </si>
@@ -354,6 +354,93 @@
   </si>
   <si>
     <t>2025-04-11T04:14:09.780637500Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:11:31.747272700Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:16:37.738380900Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:18:55.945082700Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:20:23.672548400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:38:58.774716100Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:40:07.236171400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:43:35.979567300Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:44:39.238952800Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:50:23.818697300Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:53:22.692664Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:55:20.355776400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:56:40.359963900Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:57:46.800386400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T07:59:12.890204400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:01:14.357325300Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:04:03.996944300Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:08:25.778081400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:09:28.041746400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:15:07.315759800Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:17:43.104085500Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:20:21.935600300Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:25:51.704491300Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:26:17.513149200Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:26:20.055288100Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:28:07.423006800Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:30:54.379959400Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:48:46.516742200Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:55:16.831362100Z</t>
+  </si>
+  <si>
+    <t>2025-04-11T08:56:16.843420700Z</t>
   </si>
 </sst>
 </file>
@@ -726,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="13.44140625"/>
@@ -1884,6 +1971,325 @@
         <v>106</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B112" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B113" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B114" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B115" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B116" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B117" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B118" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B119" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B120" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B121" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B122" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B123" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B124" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C124" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B125" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C125" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B126" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C126" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B127" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C127" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B128" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C128" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B129" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C129" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B130" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C130" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B131" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C131" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B132" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C132" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B133" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C133" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B134" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C134" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B135" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="C135" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B136" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C136" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B137" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C137" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B138" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C138" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B139" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C139" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="B140" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="C140" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
